--- a/salidas/empresas/USB.xlsx
+++ b/salidas/empresas/USB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.44505882263184</v>
+        <v>15.44506549835205</v>
       </c>
       <c r="C2" t="n">
         <v>29.90999984741211</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96145343780518</v>
+        <v>15.96145629882812</v>
       </c>
       <c r="C3" t="n">
         <v>30.90999984741211</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>15.92076301574707</v>
+        <v>15.92075634002686</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.41143989562988</v>
+        <v>16.41143608093262</v>
       </c>
       <c r="C5" t="n">
         <v>31.44000053405762</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>16.1138973236084</v>
+        <v>16.1138858795166</v>
       </c>
       <c r="C6" t="n">
         <v>30.8700008392334</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>16.29255485534668</v>
+        <v>16.29254722595215</v>
       </c>
       <c r="C7" t="n">
         <v>30.8799991607666</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.92041397094727</v>
+        <v>16.9204044342041</v>
       </c>
       <c r="C9" t="n">
         <v>32.06999969482422</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>17.70275115966797</v>
+        <v>17.70275497436523</v>
       </c>
       <c r="C10" t="n">
         <v>33.22000122070312</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>18.03314208984375</v>
+        <v>18.03314399719238</v>
       </c>
       <c r="C11" t="n">
         <v>33.84000015258789</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>17.92656135559082</v>
+        <v>17.92656517028809</v>
       </c>
       <c r="C12" t="n">
         <v>33.63999938964844</v>
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>19.18014335632324</v>
+        <v>19.18013763427734</v>
       </c>
       <c r="C14" t="n">
         <v>35.59999847412109</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.21246719360352</v>
+        <v>19.21246910095215</v>
       </c>
       <c r="C15" t="n">
         <v>35.65999984741211</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.05481719970703</v>
+        <v>19.05481338500977</v>
       </c>
       <c r="C16" t="n">
         <v>34.97000122070312</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>18.71698188781738</v>
+        <v>18.71698760986328</v>
       </c>
       <c r="C17" t="n">
         <v>34.34999847412109</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>18.84231567382812</v>
+        <v>18.84231376647949</v>
       </c>
       <c r="C18" t="n">
         <v>34.58000183105469</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>18.17111206054688</v>
+        <v>18.17110252380371</v>
       </c>
       <c r="C19" t="n">
         <v>32.95000076293945</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>16.51669120788574</v>
+        <v>16.51668167114258</v>
       </c>
       <c r="C20" t="n">
         <v>29.95000076293945</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.16054916381836</v>
+        <v>18.16055107116699</v>
       </c>
       <c r="C22" t="n">
         <v>32.52999877929688</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>18.51227188110352</v>
+        <v>18.51226425170898</v>
       </c>
       <c r="C23" t="n">
         <v>33.15999984741211</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>18.47319030761719</v>
+        <v>18.47317886352539</v>
       </c>
       <c r="C24" t="n">
         <v>33.09000015258789</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.95401000976562</v>
+        <v>17.95401573181152</v>
       </c>
       <c r="C25" t="n">
         <v>31.73999977111816</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>18.11240386962891</v>
+        <v>18.11239624023438</v>
       </c>
       <c r="C27" t="n">
         <v>32.02000045776367</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>18.53712844848633</v>
+        <v>18.53712463378906</v>
       </c>
       <c r="C28" t="n">
         <v>32.36000061035156</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>19.41357040405273</v>
+        <v>19.4135684967041</v>
       </c>
       <c r="C29" t="n">
         <v>33.88999938964844</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>19.0125789642334</v>
+        <v>19.0125732421875</v>
       </c>
       <c r="C30" t="n">
         <v>33.18999862670898</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.20657348632812</v>
+        <v>16.20658302307129</v>
       </c>
       <c r="C31" t="n">
         <v>27.88999938964844</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.78714561462402</v>
+        <v>17.78713607788086</v>
       </c>
       <c r="C32" t="n">
         <v>30.61000061035156</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>18.51350402832031</v>
+        <v>18.51350784301758</v>
       </c>
       <c r="C33" t="n">
         <v>31.86000061035156</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>21.18583488464355</v>
+        <v>21.18582916259766</v>
       </c>
       <c r="C34" t="n">
         <v>36.02000045776367</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>17.53329849243164</v>
+        <v>17.53330230712891</v>
       </c>
       <c r="C35" t="n">
         <v>29.80999946594238</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.86878490447998</v>
+        <v>15.86878681182861</v>
       </c>
       <c r="C36" t="n">
         <v>26.97999954223633</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>14.97249794006348</v>
+        <v>14.97249603271484</v>
       </c>
       <c r="C37" t="n">
         <v>25.01000022888184</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.884121894836426</v>
+        <v>8.884123802185059</v>
       </c>
       <c r="C38" t="n">
         <v>14.84000015258789</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.566835403442383</v>
+        <v>8.566830635070801</v>
       </c>
       <c r="C39" t="n">
         <v>14.3100004196167</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.772759437561035</v>
+        <v>8.772757530212402</v>
       </c>
       <c r="C40" t="n">
         <v>14.60999965667725</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.94043064117432</v>
+        <v>10.9404296875</v>
       </c>
       <c r="C41" t="n">
         <v>18.21999931335449</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.52888584136963</v>
+        <v>11.52888298034668</v>
       </c>
       <c r="C42" t="n">
         <v>19.20000076293945</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.79061412811279</v>
+        <v>10.79061508178711</v>
       </c>
       <c r="C43" t="n">
         <v>17.92000007629395</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>12.2899866104126</v>
+        <v>12.28998279571533</v>
       </c>
       <c r="C44" t="n">
         <v>20.40999984741211</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.62074947357178</v>
+        <v>13.6207447052002</v>
       </c>
       <c r="C45" t="n">
         <v>22.6200008392334</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.19301414489746</v>
+        <v>13.19301700592041</v>
       </c>
       <c r="C46" t="n">
         <v>21.86000061035156</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.01380443572998</v>
+        <v>14.01379871368408</v>
       </c>
       <c r="C47" t="n">
         <v>23.21999931335449</v>
@@ -1374,11 +1386,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>14.56300830841064</v>
+        <v>14.56301021575928</v>
       </c>
       <c r="C48" t="n">
         <v>24.1299991607666</v>
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.61559391021729</v>
+        <v>13.61559963226318</v>
       </c>
       <c r="C49" t="n">
         <v>22.51000022888184</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.17011070251465</v>
+        <v>15.17011260986328</v>
       </c>
       <c r="C50" t="n">
         <v>25.07999992370605</v>
@@ -1449,11 +1461,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>14.88582420349121</v>
+        <v>14.88582611083984</v>
       </c>
       <c r="C51" t="n">
         <v>24.61000061035156</v>
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>15.68411540985107</v>
+        <v>15.68411350250244</v>
       </c>
       <c r="C52" t="n">
         <v>25.8799991607666</v>
@@ -1499,11 +1511,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.22347450256348</v>
+        <v>16.22348213195801</v>
       </c>
       <c r="C53" t="n">
         <v>26.77000045776367</v>
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.57386684417725</v>
+        <v>13.57387447357178</v>
       </c>
       <c r="C55" t="n">
         <v>22.35000038146973</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.51523494720459</v>
+        <v>14.51523590087891</v>
       </c>
       <c r="C56" t="n">
         <v>23.89999961853027</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.63250541687012</v>
+        <v>12.63250923156738</v>
       </c>
       <c r="C57" t="n">
         <v>20.79999923706055</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>13.16062545776367</v>
+        <v>13.16062450408936</v>
       </c>
       <c r="C58" t="n">
         <v>21.6200008392334</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>14.73112773895264</v>
+        <v>14.7311315536499</v>
       </c>
       <c r="C59" t="n">
         <v>24.20000076293945</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>14.47546100616455</v>
+        <v>14.4754695892334</v>
       </c>
       <c r="C60" t="n">
         <v>23.78000068664551</v>
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1724,7 +1736,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1749,11 +1761,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>16.91103553771973</v>
+        <v>16.91103744506836</v>
       </c>
       <c r="C63" t="n">
         <v>27.72999954223633</v>
@@ -1778,11 +1790,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>16.19357490539551</v>
+        <v>16.19357109069824</v>
       </c>
       <c r="C64" t="n">
         <v>26.43000030517578</v>
@@ -1807,11 +1819,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.81981563568115</v>
+        <v>15.81982517242432</v>
       </c>
       <c r="C65" t="n">
         <v>25.81999969482422</v>
@@ -1836,11 +1848,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>15.68503284454346</v>
+        <v>15.68503379821777</v>
       </c>
       <c r="C66" t="n">
         <v>25.60000038146973</v>
@@ -1865,11 +1877,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>15.70981597900391</v>
+        <v>15.70981216430664</v>
       </c>
       <c r="C67" t="n">
         <v>25.51000022888184</v>
@@ -1894,11 +1906,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>16.04851913452148</v>
+        <v>16.04851531982422</v>
       </c>
       <c r="C68" t="n">
         <v>26.05999946594238</v>
@@ -1923,11 +1935,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>14.29340648651123</v>
+        <v>14.29340267181396</v>
       </c>
       <c r="C69" t="n">
         <v>23.20999908447266</v>
@@ -1952,11 +1964,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.57230854034424</v>
+        <v>14.57230281829834</v>
       </c>
       <c r="C70" t="n">
         <v>23.54000091552734</v>
@@ -1981,11 +1993,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.84134864807129</v>
+        <v>15.84134483337402</v>
       </c>
       <c r="C71" t="n">
         <v>25.59000015258789</v>
@@ -2010,11 +2022,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>16.04563903808594</v>
+        <v>16.04563140869141</v>
       </c>
       <c r="C72" t="n">
         <v>25.92000007629395</v>
@@ -2039,7 +2051,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2068,11 +2080,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>17.54976272583008</v>
+        <v>17.54975891113281</v>
       </c>
       <c r="C74" t="n">
         <v>28.21999931335449</v>
@@ -2097,11 +2109,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>18.28358268737793</v>
+        <v>18.28359222412109</v>
       </c>
       <c r="C75" t="n">
         <v>29.39999961853027</v>
@@ -2126,11 +2138,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>19.82347679138184</v>
+        <v>19.82348442077637</v>
       </c>
       <c r="C76" t="n">
         <v>31.68000030517578</v>
@@ -2155,11 +2167,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>20.13009834289551</v>
+        <v>20.13009643554688</v>
       </c>
       <c r="C77" t="n">
         <v>32.16999816894531</v>
@@ -2184,11 +2196,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>19.4668083190918</v>
+        <v>19.46680641174316</v>
       </c>
       <c r="C78" t="n">
         <v>31.11000061035156</v>
@@ -2213,11 +2225,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>20.24995613098145</v>
+        <v>20.24994850158691</v>
       </c>
       <c r="C79" t="n">
         <v>32.15999984741211</v>
@@ -2242,11 +2254,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>21.09370040893555</v>
+        <v>21.09370231628418</v>
       </c>
       <c r="C80" t="n">
         <v>33.5</v>
@@ -2271,11 +2283,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>21.03702545166016</v>
+        <v>21.03703498840332</v>
       </c>
       <c r="C81" t="n">
         <v>33.40999984741211</v>
@@ -2300,11 +2312,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>21.7215747833252</v>
+        <v>21.72157287597656</v>
       </c>
       <c r="C82" t="n">
         <v>34.29999923706055</v>
@@ -2329,11 +2341,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>21.03130149841309</v>
+        <v>21.03129386901855</v>
       </c>
       <c r="C83" t="n">
         <v>33.20999908447266</v>
@@ -2358,11 +2370,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>20.4296817779541</v>
+        <v>20.42967414855957</v>
       </c>
       <c r="C84" t="n">
         <v>32.2599983215332</v>
@@ -2387,11 +2399,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>20.35003280639648</v>
+        <v>20.35004234313965</v>
       </c>
       <c r="C85" t="n">
         <v>31.94000053405762</v>
@@ -2416,11 +2428,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>21.08911323547363</v>
+        <v>21.089111328125</v>
       </c>
       <c r="C86" t="n">
         <v>33.09999847412109</v>
@@ -2445,11 +2457,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>21.64978790283203</v>
+        <v>21.6497859954834</v>
       </c>
       <c r="C87" t="n">
         <v>33.97999954223633</v>
@@ -2474,11 +2486,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>21.74385643005371</v>
+        <v>21.74386215209961</v>
       </c>
       <c r="C88" t="n">
         <v>33.93000030517578</v>
@@ -2503,11 +2515,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>21.32731246948242</v>
+        <v>21.32730865478516</v>
       </c>
       <c r="C89" t="n">
         <v>33.27999877929688</v>
@@ -2532,11 +2544,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>22.46802139282227</v>
+        <v>22.46801948547363</v>
       </c>
       <c r="C90" t="n">
         <v>35.06000137329102</v>
@@ -2561,11 +2573,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>23.31574440002441</v>
+        <v>23.31574630737305</v>
       </c>
       <c r="C91" t="n">
         <v>36.15000152587891</v>
@@ -2590,11 +2602,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>24.07037353515625</v>
+        <v>24.07036590576172</v>
       </c>
       <c r="C92" t="n">
         <v>37.31999969482422</v>
@@ -2619,11 +2631,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>23.30285453796387</v>
+        <v>23.3028564453125</v>
       </c>
       <c r="C93" t="n">
         <v>36.13000106811523</v>
@@ -2648,11 +2660,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>23.74163627624512</v>
+        <v>23.74163436889648</v>
       </c>
       <c r="C94" t="n">
         <v>36.58000183105469</v>
@@ -2677,11 +2689,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>24.24788093566895</v>
+        <v>24.24786949157715</v>
       </c>
       <c r="C95" t="n">
         <v>37.36000061035156</v>
@@ -2706,11 +2718,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>25.45507431030273</v>
+        <v>25.4550838470459</v>
       </c>
       <c r="C96" t="n">
         <v>39.22000122070312</v>
@@ -2735,11 +2747,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>26.3706226348877</v>
+        <v>26.37062454223633</v>
       </c>
       <c r="C97" t="n">
         <v>40.40000152587891</v>
@@ -2764,11 +2776,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>25.93328666687012</v>
+        <v>25.93328094482422</v>
       </c>
       <c r="C98" t="n">
         <v>39.72999954223633</v>
@@ -2793,7 +2805,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2822,11 +2834,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>28.1270809173584</v>
+        <v>28.1270923614502</v>
       </c>
       <c r="C100" t="n">
         <v>42.86000061035156</v>
@@ -2851,11 +2863,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>26.76208305358887</v>
+        <v>26.76208686828613</v>
       </c>
       <c r="C101" t="n">
         <v>40.77999877929688</v>
@@ -2880,11 +2892,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>27.68739891052246</v>
+        <v>27.68739128112793</v>
       </c>
       <c r="C102" t="n">
         <v>42.18999862670898</v>
@@ -2909,11 +2921,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>28.59049797058105</v>
+        <v>28.59051895141602</v>
       </c>
       <c r="C103" t="n">
         <v>43.31999969482422</v>
@@ -2938,7 +2950,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2967,11 +2979,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>27.90413093566895</v>
+        <v>27.90413284301758</v>
       </c>
       <c r="C105" t="n">
         <v>42.27999877929688</v>
@@ -2996,11 +3008,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>27.76963043212891</v>
+        <v>27.76962661743164</v>
       </c>
       <c r="C106" t="n">
         <v>41.83000183105469</v>
@@ -3025,11 +3037,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>28.28080558776855</v>
+        <v>28.28081130981445</v>
       </c>
       <c r="C107" t="n">
         <v>42.59999847412109</v>
@@ -3054,11 +3066,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>29.3430004119873</v>
+        <v>29.34300422668457</v>
       </c>
       <c r="C108" t="n">
         <v>44.20000076293945</v>
@@ -3083,11 +3095,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.00159072875977</v>
+        <v>30.00160026550293</v>
       </c>
       <c r="C109" t="n">
         <v>44.95000076293945</v>
@@ -3112,11 +3124,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>27.97257614135742</v>
+        <v>27.97257041931152</v>
       </c>
       <c r="C110" t="n">
         <v>41.90999984741211</v>
@@ -3141,11 +3153,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>29.77466011047363</v>
+        <v>29.77468109130859</v>
       </c>
       <c r="C111" t="n">
         <v>44.61000061035156</v>
@@ -3170,11 +3182,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>29.31333160400391</v>
+        <v>29.31330299377441</v>
       </c>
       <c r="C112" t="n">
         <v>43.66999816894531</v>
@@ -3199,11 +3211,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>28.77632141113281</v>
+        <v>28.77632904052734</v>
       </c>
       <c r="C113" t="n">
         <v>42.86999893188477</v>
@@ -3228,11 +3240,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>28.93743133544922</v>
+        <v>28.93741798400879</v>
       </c>
       <c r="C114" t="n">
         <v>43.11000061035156</v>
@@ -3257,11 +3269,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>29.29976081848145</v>
+        <v>29.29976272583008</v>
       </c>
       <c r="C115" t="n">
         <v>43.40000152587891</v>
@@ -3286,7 +3298,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3315,11 +3327,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>28.59089851379395</v>
+        <v>28.59087944030762</v>
       </c>
       <c r="C117" t="n">
         <v>42.34999847412109</v>
@@ -3344,11 +3356,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>27.85672187805176</v>
+        <v>27.85671043395996</v>
       </c>
       <c r="C118" t="n">
         <v>41.0099983215332</v>
@@ -3373,11 +3385,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>28.65146064758301</v>
+        <v>28.65146446228027</v>
       </c>
       <c r="C119" t="n">
         <v>42.18000030517578</v>
@@ -3402,11 +3414,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>29.81300926208496</v>
+        <v>29.81300163269043</v>
       </c>
       <c r="C120" t="n">
         <v>43.88999938964844</v>
@@ -3431,11 +3443,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>29.1569995880127</v>
+        <v>29.15699577331543</v>
       </c>
       <c r="C121" t="n">
         <v>42.66999816894531</v>
@@ -3460,11 +3472,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>27.37356185913086</v>
+        <v>27.37355804443359</v>
       </c>
       <c r="C122" t="n">
         <v>40.06000137329102</v>
@@ -3489,11 +3501,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>26.32125091552734</v>
+        <v>26.32125663757324</v>
       </c>
       <c r="C123" t="n">
         <v>38.52000045776367</v>
@@ -3518,11 +3530,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>27.91062355041504</v>
+        <v>27.91061782836914</v>
       </c>
       <c r="C124" t="n">
         <v>40.59000015258789</v>
@@ -3547,7 +3559,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3576,11 +3588,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>29.44401550292969</v>
+        <v>29.44402885437012</v>
       </c>
       <c r="C126" t="n">
         <v>42.81999969482422</v>
@@ -3605,11 +3617,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>27.91583442687988</v>
+        <v>27.91583251953125</v>
       </c>
       <c r="C127" t="n">
         <v>40.33000183105469</v>
@@ -3634,11 +3646,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>29.18944931030273</v>
+        <v>29.18945503234863</v>
       </c>
       <c r="C128" t="n">
         <v>42.16999816894531</v>
@@ -3663,11 +3675,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>30.55998229980469</v>
+        <v>30.55998802185059</v>
       </c>
       <c r="C129" t="n">
         <v>44.15000152587891</v>
@@ -3692,11 +3704,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>29.88286399841309</v>
+        <v>29.88285827636719</v>
       </c>
       <c r="C130" t="n">
         <v>42.88999938964844</v>
@@ -3721,11 +3733,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>31.18575286865234</v>
+        <v>31.18575859069824</v>
       </c>
       <c r="C131" t="n">
         <v>44.7599983215332</v>
@@ -3750,11 +3762,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>34.57188415527344</v>
+        <v>34.57187271118164</v>
       </c>
       <c r="C132" t="n">
         <v>49.61999893188477</v>
@@ -3779,11 +3791,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>35.9837646484375</v>
+        <v>35.98377227783203</v>
       </c>
       <c r="C133" t="n">
         <v>51.36999893188477</v>
@@ -3808,7 +3820,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3837,11 +3849,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>38.52652359008789</v>
+        <v>38.52651977539062</v>
       </c>
       <c r="C135" t="n">
         <v>55</v>
@@ -3866,7 +3878,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3895,11 +3907,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.11255645751953</v>
+        <v>36.112548828125</v>
       </c>
       <c r="C137" t="n">
         <v>51.27999877929688</v>
@@ -3924,11 +3936,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>35.8379020690918</v>
+        <v>35.83791351318359</v>
       </c>
       <c r="C138" t="n">
         <v>50.88999938964844</v>
@@ -3953,7 +3965,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3982,7 +3994,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4011,11 +4023,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>36.28903961181641</v>
+        <v>36.28903579711914</v>
       </c>
       <c r="C141" t="n">
         <v>51.25</v>
@@ -4040,11 +4052,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>38.15734481811523</v>
+        <v>38.15734100341797</v>
       </c>
       <c r="C142" t="n">
         <v>53.59000015258789</v>
@@ -4069,11 +4081,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>38.71984100341797</v>
+        <v>38.7198371887207</v>
       </c>
       <c r="C143" t="n">
         <v>54.38000106811523</v>
@@ -4098,11 +4110,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>39.26810455322266</v>
+        <v>39.26809310913086</v>
       </c>
       <c r="C144" t="n">
         <v>55.15000152587891</v>
@@ -4127,7 +4139,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4156,11 +4168,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>40.91201782226562</v>
+        <v>40.91202163696289</v>
       </c>
       <c r="C146" t="n">
         <v>57.13999938964844</v>
@@ -4185,11 +4197,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>38.92155456542969</v>
+        <v>38.92154693603516</v>
       </c>
       <c r="C147" t="n">
         <v>54.36000061035156</v>
@@ -4214,11 +4226,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>36.37667083740234</v>
+        <v>36.37666320800781</v>
       </c>
       <c r="C148" t="n">
         <v>50.5</v>
@@ -4243,11 +4255,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>36.34066390991211</v>
+        <v>36.34065628051758</v>
       </c>
       <c r="C149" t="n">
         <v>50.45000076293945</v>
@@ -4272,11 +4284,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>36.00930786132812</v>
+        <v>36.00931549072266</v>
       </c>
       <c r="C150" t="n">
         <v>49.9900016784668</v>
@@ -4301,11 +4313,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>36.2491569519043</v>
+        <v>36.24915313720703</v>
       </c>
       <c r="C151" t="n">
         <v>50.02000045776367</v>
@@ -4330,7 +4342,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4359,11 +4371,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>39.21316528320312</v>
+        <v>39.21316146850586</v>
       </c>
       <c r="C153" t="n">
         <v>54.11000061035156</v>
@@ -4388,11 +4400,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>38.53702163696289</v>
+        <v>38.53703689575195</v>
       </c>
       <c r="C154" t="n">
         <v>52.81000137329102</v>
@@ -4417,11 +4429,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>38.14297866821289</v>
+        <v>38.14297485351562</v>
       </c>
       <c r="C155" t="n">
         <v>52.27000045776367</v>
@@ -4446,11 +4458,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>39.74106979370117</v>
+        <v>39.74107360839844</v>
       </c>
       <c r="C156" t="n">
         <v>54.45999908447266</v>
@@ -4475,11 +4487,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>33.62115097045898</v>
+        <v>33.62114715576172</v>
       </c>
       <c r="C157" t="n">
         <v>45.70000076293945</v>
@@ -4504,11 +4516,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>37.63803100585938</v>
+        <v>37.63803482055664</v>
       </c>
       <c r="C158" t="n">
         <v>51.15999984741211</v>
@@ -4533,11 +4545,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>38.02794647216797</v>
+        <v>38.0279541015625</v>
       </c>
       <c r="C159" t="n">
         <v>51.68999862670898</v>
@@ -4562,11 +4574,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.7276725769043</v>
+        <v>35.72768783569336</v>
       </c>
       <c r="C160" t="n">
         <v>48.18999862670898</v>
@@ -4591,11 +4603,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.53102111816406</v>
+        <v>39.53101348876953</v>
       </c>
       <c r="C161" t="n">
         <v>53.31999969482422</v>
@@ -4620,7 +4632,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4649,11 +4661,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>39.12744903564453</v>
+        <v>39.12746047973633</v>
       </c>
       <c r="C163" t="n">
         <v>52.40000152587891</v>
@@ -4678,11 +4690,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>42.67432403564453</v>
+        <v>42.67431259155273</v>
       </c>
       <c r="C164" t="n">
         <v>57.15000152587891</v>
@@ -4707,11 +4719,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>39.34399032592773</v>
+        <v>39.343994140625</v>
       </c>
       <c r="C165" t="n">
         <v>52.68999862670898</v>
@@ -4736,7 +4748,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4765,11 +4777,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>42.90149307250977</v>
+        <v>42.9014892578125</v>
       </c>
       <c r="C167" t="n">
         <v>57.02000045776367</v>
@@ -4794,11 +4806,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>45.16619491577148</v>
+        <v>45.16618347167969</v>
       </c>
       <c r="C168" t="n">
         <v>60.02999877929688</v>
@@ -4823,7 +4835,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4852,7 +4864,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4881,11 +4893,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>35.18859481811523</v>
+        <v>35.1885986328125</v>
       </c>
       <c r="C171" t="n">
         <v>46.43999862670898</v>
@@ -4910,11 +4922,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>26.41365242004395</v>
+        <v>26.41365814208984</v>
       </c>
       <c r="C172" t="n">
         <v>34.45000076293945</v>
@@ -4939,11 +4951,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>27.98544311523438</v>
+        <v>27.98544120788574</v>
       </c>
       <c r="C173" t="n">
         <v>36.5</v>
@@ -4968,11 +4980,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>27.26471900939941</v>
+        <v>27.26471519470215</v>
       </c>
       <c r="C174" t="n">
         <v>35.56000137329102</v>
@@ -4997,11 +5009,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>28.5634765625</v>
+        <v>28.56347465515137</v>
       </c>
       <c r="C175" t="n">
         <v>36.81999969482422</v>
@@ -5026,11 +5038,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>28.5789909362793</v>
+        <v>28.57898902893066</v>
       </c>
       <c r="C176" t="n">
         <v>36.84000015258789</v>
@@ -5055,7 +5067,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5084,11 +5096,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>28.13835906982422</v>
+        <v>28.13836669921875</v>
       </c>
       <c r="C178" t="n">
         <v>35.84999847412109</v>
@@ -5113,11 +5125,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>30.57152366638184</v>
+        <v>30.571533203125</v>
       </c>
       <c r="C179" t="n">
         <v>38.95000076293945</v>
@@ -5142,7 +5154,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5171,11 +5183,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>36.90409469604492</v>
+        <v>36.90410232543945</v>
       </c>
       <c r="C181" t="n">
         <v>46.59000015258789</v>
@@ -5200,11 +5212,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>33.94162368774414</v>
+        <v>33.9416389465332</v>
       </c>
       <c r="C182" t="n">
         <v>42.84999847412109</v>
@@ -5229,11 +5241,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>39.60517120361328</v>
+        <v>39.60516357421875</v>
       </c>
       <c r="C183" t="n">
         <v>50</v>
@@ -5258,11 +5270,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>44.14471435546875</v>
+        <v>44.14470291137695</v>
       </c>
       <c r="C184" t="n">
         <v>55.31000137329102</v>
@@ -5287,11 +5299,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>47.3691520690918</v>
+        <v>47.36916732788086</v>
       </c>
       <c r="C185" t="n">
         <v>59.34999847412109</v>
@@ -5316,11 +5328,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>48.51050186157227</v>
+        <v>48.51049041748047</v>
       </c>
       <c r="C186" t="n">
         <v>60.77999877929688</v>
@@ -5345,7 +5357,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5374,11 +5386,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>44.65422058105469</v>
+        <v>44.65422439575195</v>
       </c>
       <c r="C188" t="n">
         <v>55.54000091552734</v>
@@ -5403,11 +5415,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>46.14162445068359</v>
+        <v>46.14162063598633</v>
       </c>
       <c r="C189" t="n">
         <v>57.38999938964844</v>
@@ -5432,7 +5444,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5461,11 +5473,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>48.90990447998047</v>
+        <v>48.909912109375</v>
       </c>
       <c r="C191" t="n">
         <v>60.36999893188477</v>
@@ -5490,11 +5502,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>44.83475875854492</v>
+        <v>44.83477020263672</v>
       </c>
       <c r="C192" t="n">
         <v>55.34000015258789</v>
@@ -5519,7 +5531,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5548,11 +5560,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>47.53003692626953</v>
+        <v>47.53002548217773</v>
       </c>
       <c r="C194" t="n">
         <v>58.18999862670898</v>
@@ -5577,7 +5589,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5606,11 +5618,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>43.76734161376953</v>
+        <v>43.7673454284668</v>
       </c>
       <c r="C196" t="n">
         <v>53.15000152587891</v>
@@ -5635,11 +5647,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>39.98762512207031</v>
+        <v>39.98761749267578</v>
       </c>
       <c r="C197" t="n">
         <v>48.56000137329102</v>
@@ -5664,7 +5676,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5693,7 +5705,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5722,11 +5734,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>39.25278091430664</v>
+        <v>39.25278472900391</v>
       </c>
       <c r="C200" t="n">
         <v>47.20000076293945</v>
@@ -5751,11 +5763,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>37.93049240112305</v>
+        <v>37.93050003051758</v>
       </c>
       <c r="C201" t="n">
         <v>45.61000061035156</v>
@@ -5780,11 +5792,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>33.9243278503418</v>
+        <v>33.92432403564453</v>
       </c>
       <c r="C202" t="n">
         <v>40.31999969482422</v>
@@ -5809,11 +5821,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>35.71645736694336</v>
+        <v>35.71646118164062</v>
       </c>
       <c r="C203" t="n">
         <v>42.45000076293945</v>
@@ -5838,11 +5850,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>38.19010925292969</v>
+        <v>38.19010543823242</v>
       </c>
       <c r="C204" t="n">
         <v>45.38999938964844</v>
@@ -5867,11 +5879,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>37.10329437255859</v>
+        <v>37.10329055786133</v>
       </c>
       <c r="C205" t="n">
         <v>43.61000061035156</v>
@@ -5896,11 +5908,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>42.36972808837891</v>
+        <v>42.36972427368164</v>
       </c>
       <c r="C206" t="n">
         <v>49.79999923706055</v>
@@ -5925,11 +5937,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>40.60857772827148</v>
+        <v>40.60857009887695</v>
       </c>
       <c r="C207" t="n">
         <v>47.72999954223633</v>
@@ -5954,11 +5966,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>31.08317947387695</v>
+        <v>31.08318138122559</v>
       </c>
       <c r="C208" t="n">
         <v>36.04999923706055</v>
@@ -5983,11 +5995,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>29.55704116821289</v>
+        <v>29.55704879760742</v>
       </c>
       <c r="C209" t="n">
         <v>34.27999877929688</v>
@@ -6012,11 +6024,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.7805061340332</v>
+        <v>25.78050422668457</v>
       </c>
       <c r="C210" t="n">
         <v>29.89999961853027</v>
@@ -6041,11 +6053,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>28.91735458374023</v>
+        <v>28.91735649108887</v>
       </c>
       <c r="C211" t="n">
         <v>33.04000091552734</v>
@@ -6070,11 +6082,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>34.72882843017578</v>
+        <v>34.72883605957031</v>
       </c>
       <c r="C212" t="n">
         <v>39.68000030517578</v>
@@ -6099,11 +6111,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>31.97187805175781</v>
+        <v>31.97187995910645</v>
       </c>
       <c r="C213" t="n">
         <v>36.52999877929688</v>
@@ -6128,11 +6140,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>29.36833953857422</v>
+        <v>29.36833763122559</v>
       </c>
       <c r="C214" t="n">
         <v>33.06000137329102</v>
@@ -6157,11 +6169,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>28.32010459899902</v>
+        <v>28.32010078430176</v>
       </c>
       <c r="C215" t="n">
         <v>31.8799991607666</v>
@@ -6186,11 +6198,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>33.86331176757812</v>
+        <v>33.86330795288086</v>
       </c>
       <c r="C216" t="n">
         <v>38.11999893188477</v>
@@ -6215,11 +6227,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>38.88069152832031</v>
+        <v>38.88069534301758</v>
       </c>
       <c r="C217" t="n">
         <v>43.27999877929688</v>
@@ -6244,11 +6256,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>37.31756591796875</v>
+        <v>37.31756973266602</v>
       </c>
       <c r="C218" t="n">
         <v>41.54000091552734</v>
@@ -6273,11 +6285,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>37.69486999511719</v>
+        <v>37.69487380981445</v>
       </c>
       <c r="C219" t="n">
         <v>41.95999908447266</v>
@@ -6302,11 +6314,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>40.61352157592773</v>
+        <v>40.61352920532227</v>
       </c>
       <c r="C220" t="n">
         <v>44.70000076293945</v>
@@ -6331,11 +6343,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>36.91561126708984</v>
+        <v>36.91560745239258</v>
       </c>
       <c r="C221" t="n">
         <v>40.63000106811523</v>
@@ -6360,7 +6372,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6389,7 +6401,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6418,7 +6430,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6447,11 +6459,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>43.44877243041992</v>
+        <v>43.44877624511719</v>
       </c>
       <c r="C225" t="n">
         <v>47.22999954223633</v>
@@ -6476,11 +6488,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>42.53650665283203</v>
+        <v>42.53650283813477</v>
       </c>
       <c r="C226" t="n">
         <v>45.72999954223633</v>
@@ -6505,7 +6517,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6534,11 +6546,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>49.56855773925781</v>
+        <v>49.56856155395508</v>
       </c>
       <c r="C228" t="n">
         <v>53.29000091552734</v>
@@ -6563,11 +6575,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>44.95571136474609</v>
+        <v>44.95571517944336</v>
       </c>
       <c r="C229" t="n">
         <v>47.83000183105469</v>
@@ -6592,7 +6604,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6621,11 +6633,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>44.08160400390625</v>
+        <v>44.08160018920898</v>
       </c>
       <c r="C231" t="n">
         <v>46.90000152587891</v>
@@ -6650,7 +6662,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6679,11 +6691,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>38.36979293823242</v>
+        <v>38.36978912353516</v>
       </c>
       <c r="C233" t="n">
         <v>40.34000015258789</v>
@@ -6708,11 +6720,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>41.46105575561523</v>
+        <v>41.4610595703125</v>
       </c>
       <c r="C234" t="n">
         <v>43.59000015258789</v>
@@ -6737,7 +6749,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6766,11 +6778,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>43.23657608032227</v>
+        <v>43.236572265625</v>
       </c>
       <c r="C236" t="n">
         <v>44.95999908447266</v>
@@ -6795,11 +6807,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>46.95822906494141</v>
+        <v>46.95823287963867</v>
       </c>
       <c r="C237" t="n">
         <v>48.83000183105469</v>
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6853,7 +6865,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6882,7 +6894,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6911,7 +6923,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6940,7 +6952,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6969,7 +6981,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6998,7 +7010,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7027,7 +7039,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7056,7 +7068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7085,7 +7097,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7114,7 +7126,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7143,7 +7155,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7172,32 +7184,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>58.47999954223633</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="C250" t="n">
-        <v>58.47999954223633</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="D250" t="n">
-        <v>127525400</v>
+        <v>134608600</v>
       </c>
       <c r="E250" t="n">
         <v>5.01</v>
       </c>
       <c r="F250" t="n">
-        <v>11.67265459924877</v>
+        <v>11.65668693131316</v>
       </c>
       <c r="G250" t="n">
         <v>1558051446</v>
       </c>
       <c r="H250" t="n">
-        <v>91114847848.86066</v>
+        <v>90990206823.79784</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08184928702283685</v>
+        <v>0.08639547836856216</v>
       </c>
     </row>
   </sheetData>
@@ -7229,75 +7241,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7333,13 +7345,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7375,13 +7387,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7459,13 +7471,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7585,13 +7597,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I10" t="n">
         <v>1.73</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I11" t="n">
         <v>1.91</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K11" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I12" t="n">
         <v>2.06</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="K12" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I13" t="n">
         <v>2.25</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="K13" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I14" t="n">
         <v>2.46</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K14" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I15" t="n">
         <v>2.61</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="K15" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I16" t="n">
         <v>2.72</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="K16" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I17" t="n">
         <v>2.82</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="K17" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I18" t="n">
         <v>2.84</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K18" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41273</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I19" t="n">
         <v>2.899999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K19" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I20" t="n">
         <v>2.95</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K20" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I21" t="n">
         <v>2.97</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="K21" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I22" t="n">
         <v>3</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K22" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I23" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="K23" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I24" t="n">
         <v>3.02</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K24" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I25" t="n">
         <v>3.04</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K25" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I26" t="n">
         <v>3.08</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K26" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I27" t="n">
         <v>3.11</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K27" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I28" t="n">
         <v>3.13</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="K28" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I29" t="n">
         <v>3.16</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K29" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I30" t="n">
         <v>3.16</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K30" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I31" t="n">
         <v>3.16</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K31" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I32" t="n">
         <v>3.19</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K32" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I33" t="n">
         <v>3.22</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K33" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I34" t="n">
         <v>3.240000000000001</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K34" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I35" t="n">
         <v>3.3</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="K35" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I36" t="n">
         <v>3.320000000000001</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="K36" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I37" t="n">
         <v>3.36</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="K37" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I38" t="n">
         <v>3.51</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K38" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I39" t="n">
         <v>3.65</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K39" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I40" t="n">
         <v>3.82</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K40" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I41" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="K41" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I42" t="n">
         <v>4.14</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K42" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I43" t="n">
         <v>4.18</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="K43" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I44" t="n">
         <v>4.25</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="K44" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I45" t="n">
         <v>4.34</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="K45" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I46" t="n">
         <v>4.16</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="K46" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I47" t="n">
         <v>3.88</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K47" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I48" t="n">
         <v>3.2</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K48" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I49" t="n">
         <v>3.04</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K49" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I50" t="n">
         <v>3.06</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K50" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I51" t="n">
         <v>3.79</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="K51" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I52" t="n">
         <v>4.66</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="K52" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I53" t="n">
         <v>4.97</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="K53" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I54" t="n">
         <v>5.099999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K54" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I55" t="n">
         <v>4.64</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="K55" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I56" t="n">
         <v>4.35</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K56" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I57" t="n">
         <v>4.209999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K57" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I58" t="n">
         <v>3.69</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="K58" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I59" t="n">
         <v>3.74</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="K59" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I60" t="n">
         <v>3.59</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="K60" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I61" t="n">
         <v>3.34</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K61" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I62" t="n">
         <v>3.27</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K62" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I63" t="n">
         <v>3.01</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K63" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I64" t="n">
         <v>3.14</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="K64" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I65" t="n">
         <v>3.26</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="K65" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I66" t="n">
         <v>3.79</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="K66" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I67" t="n">
         <v>4.039999999999999</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K67" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I68" t="n">
         <v>4.18</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="K68" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I69" t="n">
         <v>4.369999999999999</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="K69" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I70" t="n">
         <v>4.619999999999999</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="K70" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I71" t="n">
         <v>4.77</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="K71" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I72" t="n">
         <v>5.01</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K72" t="n">
@@ -10549,52 +10561,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40035</v>
       </c>
       <c r="C2" t="n">
@@ -10623,10 +10635,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10655,10 +10667,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40490</v>
       </c>
       <c r="C6" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C7" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="C8" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40763</v>
       </c>
       <c r="C9" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40851</v>
       </c>
       <c r="C10" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C11" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41036</v>
       </c>
       <c r="C12" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41124</v>
       </c>
       <c r="C13" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41218</v>
       </c>
       <c r="C14" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C15" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C16" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C17" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="C18" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C19" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41766</v>
       </c>
       <c r="C20" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C21" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C22" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C23" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C24" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42221</v>
       </c>
       <c r="C25" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C26" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C27" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C28" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C29" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C30" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C31" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42860</v>
       </c>
       <c r="C32" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42951</v>
       </c>
       <c r="C33" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43042</v>
       </c>
       <c r="C34" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C35" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C36" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C37" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43406</v>
       </c>
       <c r="C38" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C39" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43594</v>
       </c>
       <c r="C40" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43678</v>
       </c>
       <c r="C41" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43777</v>
       </c>
       <c r="C42" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43881</v>
       </c>
       <c r="C43" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C44" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C45" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C46" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C47" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44320</v>
       </c>
       <c r="C48" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44411</v>
       </c>
       <c r="C49" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44502</v>
       </c>
       <c r="C50" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C51" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44684</v>
       </c>
       <c r="C52" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C53" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C54" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44984</v>
       </c>
       <c r="C55" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45054</v>
       </c>
       <c r="C56" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45145</v>
       </c>
       <c r="C57" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C58" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C59" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C60" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="C61" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45601</v>
       </c>
       <c r="C62" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45709</v>
       </c>
       <c r="C63" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C64" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="C65" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45966</v>
       </c>
       <c r="C66" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46076</v>
       </c>
       <c r="C67" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="C68" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C69" t="n">
@@ -12785,12 +12797,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
@@ -12861,7 +12873,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">

--- a/salidas/empresas/USB.xlsx
+++ b/salidas/empresas/USB.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.44506549835205</v>
+        <v>15.44506454467773</v>
       </c>
       <c r="C2" t="n">
         <v>29.90999984741211</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96145629882812</v>
+        <v>15.96145534515381</v>
       </c>
       <c r="C3" t="n">
         <v>30.90999984741211</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>15.92075634002686</v>
+        <v>15.9207592010498</v>
       </c>
       <c r="C4" t="n">
         <v>30.5</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>16.41143608093262</v>
+        <v>16.41143417358398</v>
       </c>
       <c r="C5" t="n">
         <v>31.44000053405762</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>16.1138858795166</v>
+        <v>16.11389541625977</v>
       </c>
       <c r="C6" t="n">
         <v>30.8700008392334</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>16.29254722595215</v>
+        <v>16.29254913330078</v>
       </c>
       <c r="C7" t="n">
         <v>30.8799991607666</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>16.88347816467285</v>
+        <v>16.88347434997559</v>
       </c>
       <c r="C8" t="n">
         <v>32</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>16.9204044342041</v>
+        <v>16.92040824890137</v>
       </c>
       <c r="C9" t="n">
         <v>32.06999969482422</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>17.70275497436523</v>
+        <v>17.7027530670166</v>
       </c>
       <c r="C10" t="n">
         <v>33.22000122070312</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>18.03314399719238</v>
+        <v>18.03313827514648</v>
       </c>
       <c r="C11" t="n">
         <v>33.84000015258789</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>19.49801445007324</v>
+        <v>19.49802017211914</v>
       </c>
       <c r="C13" t="n">
         <v>36.18999862670898</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>19.18013763427734</v>
+        <v>19.18013954162598</v>
       </c>
       <c r="C14" t="n">
         <v>35.59999847412109</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>19.05481338500977</v>
+        <v>19.05481719970703</v>
       </c>
       <c r="C16" t="n">
         <v>34.97000122070312</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>18.71698760986328</v>
+        <v>18.71698570251465</v>
       </c>
       <c r="C17" t="n">
         <v>34.34999847412109</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>18.84231376647949</v>
+        <v>18.84230804443359</v>
       </c>
       <c r="C18" t="n">
         <v>34.58000183105469</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>18.17110252380371</v>
+        <v>18.17111587524414</v>
       </c>
       <c r="C19" t="n">
         <v>32.95000076293945</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>16.51668167114258</v>
+        <v>16.51667976379395</v>
       </c>
       <c r="C20" t="n">
         <v>29.95000076293945</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.16055107116699</v>
+        <v>18.16054916381836</v>
       </c>
       <c r="C22" t="n">
         <v>32.52999877929688</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>18.51226425170898</v>
+        <v>18.51226234436035</v>
       </c>
       <c r="C23" t="n">
         <v>33.15999984741211</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>18.47317886352539</v>
+        <v>18.47318458557129</v>
       </c>
       <c r="C24" t="n">
         <v>33.09000015258789</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>19.00048065185547</v>
+        <v>19.00048446655273</v>
       </c>
       <c r="C26" t="n">
         <v>33.59000015258789</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>18.11239624023438</v>
+        <v>18.11239814758301</v>
       </c>
       <c r="C27" t="n">
         <v>32.02000045776367</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>18.53712463378906</v>
+        <v>18.53712272644043</v>
       </c>
       <c r="C28" t="n">
         <v>32.36000061035156</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>19.4135684967041</v>
+        <v>19.41356086730957</v>
       </c>
       <c r="C29" t="n">
         <v>33.88999938964844</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>19.0125732421875</v>
+        <v>19.01257705688477</v>
       </c>
       <c r="C30" t="n">
         <v>33.18999862670898</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>16.20658302307129</v>
+        <v>16.20657348632812</v>
       </c>
       <c r="C31" t="n">
         <v>27.88999938964844</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>17.78713607788086</v>
+        <v>17.78714179992676</v>
       </c>
       <c r="C32" t="n">
         <v>30.61000061035156</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>18.51350784301758</v>
+        <v>18.51349639892578</v>
       </c>
       <c r="C33" t="n">
         <v>31.86000061035156</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>21.18582916259766</v>
+        <v>21.18583106994629</v>
       </c>
       <c r="C34" t="n">
         <v>36.02000045776367</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>17.53330230712891</v>
+        <v>17.53330039978027</v>
       </c>
       <c r="C35" t="n">
         <v>29.80999946594238</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.86878681182861</v>
+        <v>15.86878871917725</v>
       </c>
       <c r="C36" t="n">
         <v>26.97999954223633</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>8.884123802185059</v>
+        <v>8.884124755859375</v>
       </c>
       <c r="C38" t="n">
         <v>14.84000015258789</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>8.566830635070801</v>
+        <v>8.566836357116699</v>
       </c>
       <c r="C39" t="n">
         <v>14.3100004196167</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>8.772757530212402</v>
+        <v>8.772759437561035</v>
       </c>
       <c r="C40" t="n">
         <v>14.60999965667725</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>10.9404296875</v>
+        <v>10.94042778015137</v>
       </c>
       <c r="C41" t="n">
         <v>18.21999931335449</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>11.52888298034668</v>
+        <v>11.52888107299805</v>
       </c>
       <c r="C42" t="n">
         <v>19.20000076293945</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.79061508178711</v>
+        <v>10.79061794281006</v>
       </c>
       <c r="C43" t="n">
         <v>17.92000007629395</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>13.19301700592041</v>
+        <v>13.19301128387451</v>
       </c>
       <c r="C46" t="n">
         <v>21.86000061035156</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>14.01379871368408</v>
+        <v>14.01380634307861</v>
       </c>
       <c r="C47" t="n">
         <v>23.21999931335449</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>14.56301021575928</v>
+        <v>14.56300926208496</v>
       </c>
       <c r="C48" t="n">
         <v>24.1299991607666</v>
@@ -1415,7 +1415,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>13.61559963226318</v>
+        <v>13.61560153961182</v>
       </c>
       <c r="C49" t="n">
         <v>22.51000022888184</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>15.17011260986328</v>
+        <v>15.17011165618896</v>
       </c>
       <c r="C50" t="n">
         <v>25.07999992370605</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>14.88582611083984</v>
+        <v>14.88582134246826</v>
       </c>
       <c r="C51" t="n">
         <v>24.61000061035156</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.22348213195801</v>
+        <v>16.22347640991211</v>
       </c>
       <c r="C53" t="n">
         <v>26.77000045776367</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>13.57387447357178</v>
+        <v>13.57386875152588</v>
       </c>
       <c r="C55" t="n">
         <v>22.35000038146973</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>14.51523590087891</v>
+        <v>14.51523685455322</v>
       </c>
       <c r="C56" t="n">
         <v>23.89999961853027</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>12.63250923156738</v>
+        <v>12.63250541687012</v>
       </c>
       <c r="C57" t="n">
         <v>20.79999923706055</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>13.16062450408936</v>
+        <v>13.16062164306641</v>
       </c>
       <c r="C58" t="n">
         <v>21.6200008392334</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>14.7311315536499</v>
+        <v>14.73112964630127</v>
       </c>
       <c r="C59" t="n">
         <v>24.20000076293945</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>14.4754695892334</v>
+        <v>14.47546577453613</v>
       </c>
       <c r="C60" t="n">
         <v>23.78000068664551</v>
@@ -1715,7 +1715,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>16.44755554199219</v>
+        <v>16.44755172729492</v>
       </c>
       <c r="C61" t="n">
         <v>26.96999931335449</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>16.46584701538086</v>
+        <v>16.46585273742676</v>
       </c>
       <c r="C62" t="n">
         <v>27</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>16.91103744506836</v>
+        <v>16.91103553771973</v>
       </c>
       <c r="C63" t="n">
         <v>27.72999954223633</v>
@@ -1794,7 +1794,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>16.19357109069824</v>
+        <v>16.19356727600098</v>
       </c>
       <c r="C64" t="n">
         <v>26.43000030517578</v>
@@ -1823,7 +1823,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>15.81982517242432</v>
+        <v>15.81982326507568</v>
       </c>
       <c r="C65" t="n">
         <v>25.81999969482422</v>
@@ -1852,7 +1852,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>15.68503379821777</v>
+        <v>15.68502712249756</v>
       </c>
       <c r="C66" t="n">
         <v>25.60000038146973</v>
@@ -1881,7 +1881,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>15.70981216430664</v>
+        <v>15.70981407165527</v>
       </c>
       <c r="C67" t="n">
         <v>25.51000022888184</v>
@@ -1910,7 +1910,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>16.04851531982422</v>
+        <v>16.04851341247559</v>
       </c>
       <c r="C68" t="n">
         <v>26.05999946594238</v>
@@ -1939,7 +1939,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>14.29340267181396</v>
+        <v>14.29339981079102</v>
       </c>
       <c r="C69" t="n">
         <v>23.20999908447266</v>
@@ -1968,7 +1968,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>14.57230281829834</v>
+        <v>14.57230663299561</v>
       </c>
       <c r="C70" t="n">
         <v>23.54000091552734</v>
@@ -1997,7 +1997,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>15.84134483337402</v>
+        <v>15.84135055541992</v>
       </c>
       <c r="C71" t="n">
         <v>25.59000015258789</v>
@@ -2055,7 +2055,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>16.82214736938477</v>
+        <v>16.8221435546875</v>
       </c>
       <c r="C73" t="n">
         <v>27.04999923706055</v>
@@ -2084,7 +2084,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>17.54975891113281</v>
+        <v>17.54975700378418</v>
       </c>
       <c r="C74" t="n">
         <v>28.21999931335449</v>
@@ -2113,7 +2113,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>18.28359222412109</v>
+        <v>18.28359413146973</v>
       </c>
       <c r="C75" t="n">
         <v>29.39999961853027</v>
@@ -2142,7 +2142,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>19.82348442077637</v>
+        <v>19.82348251342773</v>
       </c>
       <c r="C76" t="n">
         <v>31.68000030517578</v>
@@ -2171,7 +2171,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>20.13009643554688</v>
+        <v>20.13009071350098</v>
       </c>
       <c r="C77" t="n">
         <v>32.16999816894531</v>
@@ -2229,7 +2229,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>20.24994850158691</v>
+        <v>20.24995040893555</v>
       </c>
       <c r="C79" t="n">
         <v>32.15999984741211</v>
@@ -2258,7 +2258,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>21.09370231628418</v>
+        <v>21.09370613098145</v>
       </c>
       <c r="C80" t="n">
         <v>33.5</v>
@@ -2316,7 +2316,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>21.72157287597656</v>
+        <v>21.7215747833252</v>
       </c>
       <c r="C82" t="n">
         <v>34.29999923706055</v>
@@ -2345,7 +2345,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>21.03129386901855</v>
+        <v>21.03130149841309</v>
       </c>
       <c r="C83" t="n">
         <v>33.20999908447266</v>
@@ -2374,7 +2374,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>20.42967414855957</v>
+        <v>20.42967796325684</v>
       </c>
       <c r="C84" t="n">
         <v>32.2599983215332</v>
@@ -2403,7 +2403,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>20.35004234313965</v>
+        <v>20.35003662109375</v>
       </c>
       <c r="C85" t="n">
         <v>31.94000053405762</v>
@@ -2432,7 +2432,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>21.089111328125</v>
+        <v>21.08910751342773</v>
       </c>
       <c r="C86" t="n">
         <v>33.09999847412109</v>
@@ -2461,7 +2461,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>21.6497859954834</v>
+        <v>21.6497917175293</v>
       </c>
       <c r="C87" t="n">
         <v>33.97999954223633</v>
@@ -2490,7 +2490,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>21.74386215209961</v>
+        <v>21.74385643005371</v>
       </c>
       <c r="C88" t="n">
         <v>33.93000030517578</v>
@@ -2519,7 +2519,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>21.32730865478516</v>
+        <v>21.32731056213379</v>
       </c>
       <c r="C89" t="n">
         <v>33.27999877929688</v>
@@ -2548,7 +2548,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>22.46801948547363</v>
+        <v>22.46801567077637</v>
       </c>
       <c r="C90" t="n">
         <v>35.06000137329102</v>
@@ -2577,7 +2577,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>23.31574630737305</v>
+        <v>23.31574821472168</v>
       </c>
       <c r="C91" t="n">
         <v>36.15000152587891</v>
@@ -2606,7 +2606,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>24.07036590576172</v>
+        <v>24.07036399841309</v>
       </c>
       <c r="C92" t="n">
         <v>37.31999969482422</v>
@@ -2635,7 +2635,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>23.3028564453125</v>
+        <v>23.3028450012207</v>
       </c>
       <c r="C93" t="n">
         <v>36.13000106811523</v>
@@ -2664,7 +2664,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>23.74163436889648</v>
+        <v>23.74163055419922</v>
       </c>
       <c r="C94" t="n">
         <v>36.58000183105469</v>
@@ -2693,7 +2693,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>24.24786949157715</v>
+        <v>24.24788093566895</v>
       </c>
       <c r="C95" t="n">
         <v>37.36000061035156</v>
@@ -2751,7 +2751,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>26.37062454223633</v>
+        <v>26.37061882019043</v>
       </c>
       <c r="C97" t="n">
         <v>40.40000152587891</v>
@@ -2780,7 +2780,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>25.93328094482422</v>
+        <v>25.93329048156738</v>
       </c>
       <c r="C98" t="n">
         <v>39.72999954223633</v>
@@ -2809,7 +2809,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>26.85364532470703</v>
+        <v>26.8536548614502</v>
       </c>
       <c r="C99" t="n">
         <v>41.13999938964844</v>
@@ -2838,7 +2838,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>28.1270923614502</v>
+        <v>28.12707328796387</v>
       </c>
       <c r="C100" t="n">
         <v>42.86000061035156</v>
@@ -2867,7 +2867,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>26.76208686828613</v>
+        <v>26.76207733154297</v>
       </c>
       <c r="C101" t="n">
         <v>40.77999877929688</v>
@@ -2896,7 +2896,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>27.68739128112793</v>
+        <v>27.6873950958252</v>
       </c>
       <c r="C102" t="n">
         <v>42.18999862670898</v>
@@ -2925,7 +2925,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>28.59051895141602</v>
+        <v>28.59050941467285</v>
       </c>
       <c r="C103" t="n">
         <v>43.31999969482422</v>
@@ -2954,7 +2954,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>27.73913192749023</v>
+        <v>27.7391357421875</v>
       </c>
       <c r="C104" t="n">
         <v>42.02999877929688</v>
@@ -2983,7 +2983,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>27.90413284301758</v>
+        <v>27.90413475036621</v>
       </c>
       <c r="C105" t="n">
         <v>42.27999877929688</v>
@@ -3012,7 +3012,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>27.76962661743164</v>
+        <v>27.76962852478027</v>
       </c>
       <c r="C106" t="n">
         <v>41.83000183105469</v>
@@ -3041,7 +3041,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>28.28081130981445</v>
+        <v>28.28081893920898</v>
       </c>
       <c r="C107" t="n">
         <v>42.59999847412109</v>
@@ -3070,7 +3070,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>29.34300422668457</v>
+        <v>29.34299850463867</v>
       </c>
       <c r="C108" t="n">
         <v>44.20000076293945</v>
@@ -3099,7 +3099,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>30.00160026550293</v>
+        <v>30.00159454345703</v>
       </c>
       <c r="C109" t="n">
         <v>44.95000076293945</v>
@@ -3128,7 +3128,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>27.97257041931152</v>
+        <v>27.97256851196289</v>
       </c>
       <c r="C110" t="n">
         <v>41.90999984741211</v>
@@ -3157,7 +3157,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>29.77468109130859</v>
+        <v>29.77466201782227</v>
       </c>
       <c r="C111" t="n">
         <v>44.61000061035156</v>
@@ -3186,7 +3186,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>29.31330299377441</v>
+        <v>29.31332588195801</v>
       </c>
       <c r="C112" t="n">
         <v>43.66999816894531</v>
@@ -3215,7 +3215,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>28.77632904052734</v>
+        <v>28.77632331848145</v>
       </c>
       <c r="C113" t="n">
         <v>42.86999893188477</v>
@@ -3244,7 +3244,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>28.93741798400879</v>
+        <v>28.93741416931152</v>
       </c>
       <c r="C114" t="n">
         <v>43.11000061035156</v>
@@ -3273,7 +3273,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>29.29976272583008</v>
+        <v>29.29976654052734</v>
       </c>
       <c r="C115" t="n">
         <v>43.40000152587891</v>
@@ -3302,7 +3302,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>30.52171516418457</v>
+        <v>30.52169990539551</v>
       </c>
       <c r="C116" t="n">
         <v>45.20999908447266</v>
@@ -3331,7 +3331,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>28.59087944030762</v>
+        <v>28.59089279174805</v>
       </c>
       <c r="C117" t="n">
         <v>42.34999847412109</v>
@@ -3360,7 +3360,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>27.85671043395996</v>
+        <v>27.8567066192627</v>
       </c>
       <c r="C118" t="n">
         <v>41.0099983215332</v>
@@ -3389,7 +3389,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>28.65146446228027</v>
+        <v>28.65146064758301</v>
       </c>
       <c r="C119" t="n">
         <v>42.18000030517578</v>
@@ -3418,7 +3418,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>29.81300163269043</v>
+        <v>29.81300735473633</v>
       </c>
       <c r="C120" t="n">
         <v>43.88999938964844</v>
@@ -3447,7 +3447,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>29.15699577331543</v>
+        <v>29.15700149536133</v>
       </c>
       <c r="C121" t="n">
         <v>42.66999816894531</v>
@@ -3476,7 +3476,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>27.37355804443359</v>
+        <v>27.37356758117676</v>
       </c>
       <c r="C122" t="n">
         <v>40.06000137329102</v>
@@ -3505,7 +3505,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>26.32125663757324</v>
+        <v>26.32125091552734</v>
       </c>
       <c r="C123" t="n">
         <v>38.52000045776367</v>
@@ -3534,7 +3534,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>27.91061782836914</v>
+        <v>27.91062164306641</v>
       </c>
       <c r="C124" t="n">
         <v>40.59000015258789</v>
@@ -3563,7 +3563,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>29.35463333129883</v>
+        <v>29.3546314239502</v>
       </c>
       <c r="C125" t="n">
         <v>42.68999862670898</v>
@@ -3592,7 +3592,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>29.44402885437012</v>
+        <v>29.44401931762695</v>
       </c>
       <c r="C126" t="n">
         <v>42.81999969482422</v>
@@ -3621,7 +3621,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>27.91583251953125</v>
+        <v>27.91583633422852</v>
       </c>
       <c r="C127" t="n">
         <v>40.33000183105469</v>
@@ -3650,7 +3650,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>29.18945503234863</v>
+        <v>29.18945121765137</v>
       </c>
       <c r="C128" t="n">
         <v>42.16999816894531</v>
@@ -3679,7 +3679,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>30.55998802185059</v>
+        <v>30.55997848510742</v>
       </c>
       <c r="C129" t="n">
         <v>44.15000152587891</v>
@@ -3708,7 +3708,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>29.88285827636719</v>
+        <v>29.88285636901855</v>
       </c>
       <c r="C130" t="n">
         <v>42.88999938964844</v>
@@ -3737,7 +3737,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>31.18575859069824</v>
+        <v>31.18575668334961</v>
       </c>
       <c r="C131" t="n">
         <v>44.7599983215332</v>
@@ -3795,7 +3795,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>35.98377227783203</v>
+        <v>35.98375701904297</v>
       </c>
       <c r="C133" t="n">
         <v>51.36999893188477</v>
@@ -3824,7 +3824,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>36.88039398193359</v>
+        <v>36.88038635253906</v>
       </c>
       <c r="C134" t="n">
         <v>52.65000152587891</v>
@@ -3853,7 +3853,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>38.52651977539062</v>
+        <v>38.52651596069336</v>
       </c>
       <c r="C135" t="n">
         <v>55</v>
@@ -3882,7 +3882,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>36.26748275756836</v>
+        <v>36.26747894287109</v>
       </c>
       <c r="C136" t="n">
         <v>51.5</v>
@@ -3911,7 +3911,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>36.112548828125</v>
+        <v>36.11255645751953</v>
       </c>
       <c r="C137" t="n">
         <v>51.27999877929688</v>
@@ -3940,7 +3940,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>35.83791351318359</v>
+        <v>35.83790969848633</v>
       </c>
       <c r="C138" t="n">
         <v>50.88999938964844</v>
@@ -3969,7 +3969,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>36.76345062255859</v>
+        <v>36.7634391784668</v>
       </c>
       <c r="C139" t="n">
         <v>51.91999816894531</v>
@@ -3998,7 +3998,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>37.37240219116211</v>
+        <v>37.37239837646484</v>
       </c>
       <c r="C140" t="n">
         <v>52.77999877929688</v>
@@ -4027,7 +4027,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>36.28903579711914</v>
+        <v>36.28904342651367</v>
       </c>
       <c r="C141" t="n">
         <v>51.25</v>
@@ -4085,7 +4085,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>38.7198371887207</v>
+        <v>38.7198486328125</v>
       </c>
       <c r="C143" t="n">
         <v>54.38000106811523</v>
@@ -4114,7 +4114,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>39.26809310913086</v>
+        <v>39.26810455322266</v>
       </c>
       <c r="C144" t="n">
         <v>55.15000152587891</v>
@@ -4143,7 +4143,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>38.36307144165039</v>
+        <v>38.36306762695312</v>
       </c>
       <c r="C145" t="n">
         <v>53.58000183105469</v>
@@ -4201,7 +4201,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>38.92154693603516</v>
+        <v>38.92155075073242</v>
       </c>
       <c r="C147" t="n">
         <v>54.36000061035156</v>
@@ -4230,7 +4230,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>36.37666320800781</v>
+        <v>36.37668228149414</v>
       </c>
       <c r="C148" t="n">
         <v>50.5</v>
@@ -4259,7 +4259,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>36.34065628051758</v>
+        <v>36.34066009521484</v>
       </c>
       <c r="C149" t="n">
         <v>50.45000076293945</v>
@@ -4288,7 +4288,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>36.00931549072266</v>
+        <v>36.00930786132812</v>
       </c>
       <c r="C150" t="n">
         <v>49.9900016784668</v>
@@ -4317,7 +4317,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>36.24915313720703</v>
+        <v>36.2491569519043</v>
       </c>
       <c r="C151" t="n">
         <v>50.02000045776367</v>
@@ -4346,7 +4346,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>38.41598510742188</v>
+        <v>38.41598892211914</v>
       </c>
       <c r="C152" t="n">
         <v>53.0099983215332</v>
@@ -4375,7 +4375,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>39.21316146850586</v>
+        <v>39.21315383911133</v>
       </c>
       <c r="C153" t="n">
         <v>54.11000061035156</v>
@@ -4404,7 +4404,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>38.53703689575195</v>
+        <v>38.53702163696289</v>
       </c>
       <c r="C154" t="n">
         <v>52.81000137329102</v>
@@ -4462,7 +4462,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>39.74107360839844</v>
+        <v>39.7410774230957</v>
       </c>
       <c r="C156" t="n">
         <v>54.45999908447266</v>
@@ -4491,7 +4491,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>33.62114715576172</v>
+        <v>33.62115097045898</v>
       </c>
       <c r="C157" t="n">
         <v>45.70000076293945</v>
@@ -4520,7 +4520,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>37.63803482055664</v>
+        <v>37.63802719116211</v>
       </c>
       <c r="C158" t="n">
         <v>51.15999984741211</v>
@@ -4549,7 +4549,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>38.0279541015625</v>
+        <v>38.0279426574707</v>
       </c>
       <c r="C159" t="n">
         <v>51.68999862670898</v>
@@ -4578,7 +4578,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>35.72768783569336</v>
+        <v>35.72768020629883</v>
       </c>
       <c r="C160" t="n">
         <v>48.18999862670898</v>
@@ -4636,7 +4636,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>37.2178840637207</v>
+        <v>37.21787261962891</v>
       </c>
       <c r="C162" t="n">
         <v>50.20000076293945</v>
@@ -4665,7 +4665,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>39.12746047973633</v>
+        <v>39.12745666503906</v>
       </c>
       <c r="C163" t="n">
         <v>52.40000152587891</v>
@@ -4694,7 +4694,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>42.67431259155273</v>
+        <v>42.67430877685547</v>
       </c>
       <c r="C164" t="n">
         <v>57.15000152587891</v>
@@ -4752,7 +4752,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>41.63747406005859</v>
+        <v>41.63747787475586</v>
       </c>
       <c r="C166" t="n">
         <v>55.34000015258789</v>
@@ -4781,7 +4781,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>42.9014892578125</v>
+        <v>42.9015007019043</v>
       </c>
       <c r="C167" t="n">
         <v>57.02000045776367</v>
@@ -4810,7 +4810,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>45.16618347167969</v>
+        <v>45.16619491577148</v>
       </c>
       <c r="C168" t="n">
         <v>60.02999877929688</v>
@@ -4839,7 +4839,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>44.92531967163086</v>
+        <v>44.92532348632812</v>
       </c>
       <c r="C169" t="n">
         <v>59.29000091552734</v>
@@ -4868,7 +4868,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>40.32595825195312</v>
+        <v>40.32594299316406</v>
       </c>
       <c r="C170" t="n">
         <v>53.22000122070312</v>
@@ -4897,7 +4897,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>35.1885986328125</v>
+        <v>35.18859481811523</v>
       </c>
       <c r="C171" t="n">
         <v>46.43999862670898</v>
@@ -4955,7 +4955,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>27.98544120788574</v>
+        <v>27.98543930053711</v>
       </c>
       <c r="C173" t="n">
         <v>36.5</v>
@@ -4984,7 +4984,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>27.26471519470215</v>
+        <v>27.26471900939941</v>
       </c>
       <c r="C174" t="n">
         <v>35.56000137329102</v>
@@ -5013,7 +5013,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>28.56347465515137</v>
+        <v>28.56347846984863</v>
       </c>
       <c r="C175" t="n">
         <v>36.81999969482422</v>
@@ -5042,7 +5042,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>28.57898902893066</v>
+        <v>28.57899475097656</v>
       </c>
       <c r="C176" t="n">
         <v>36.84000015258789</v>
@@ -5071,7 +5071,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>28.2376537322998</v>
+        <v>28.23766326904297</v>
       </c>
       <c r="C177" t="n">
         <v>36.40000152587891</v>
@@ -5129,7 +5129,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>30.571533203125</v>
+        <v>30.57152557373047</v>
       </c>
       <c r="C179" t="n">
         <v>38.95000076293945</v>
@@ -5216,7 +5216,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>33.9416389465332</v>
+        <v>33.94163513183594</v>
       </c>
       <c r="C182" t="n">
         <v>42.84999847412109</v>
@@ -5245,7 +5245,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>39.60516357421875</v>
+        <v>39.60517501831055</v>
       </c>
       <c r="C183" t="n">
         <v>50</v>
@@ -5274,7 +5274,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>44.14470291137695</v>
+        <v>44.14471054077148</v>
       </c>
       <c r="C184" t="n">
         <v>55.31000137329102</v>
@@ -5303,7 +5303,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>47.36916732788086</v>
+        <v>47.36915969848633</v>
       </c>
       <c r="C185" t="n">
         <v>59.34999847412109</v>
@@ -5332,7 +5332,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>48.51049041748047</v>
+        <v>48.51049423217773</v>
       </c>
       <c r="C186" t="n">
         <v>60.77999877929688</v>
@@ -5390,7 +5390,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>44.65422439575195</v>
+        <v>44.65422058105469</v>
       </c>
       <c r="C188" t="n">
         <v>55.54000091552734</v>
@@ -5419,7 +5419,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>46.14162063598633</v>
+        <v>46.14162445068359</v>
       </c>
       <c r="C189" t="n">
         <v>57.38999938964844</v>
@@ -5506,7 +5506,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>44.83477020263672</v>
+        <v>44.83475494384766</v>
       </c>
       <c r="C192" t="n">
         <v>55.34000015258789</v>
@@ -5535,7 +5535,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>45.88007736206055</v>
+        <v>45.88008499145508</v>
       </c>
       <c r="C193" t="n">
         <v>56.16999816894531</v>
@@ -5564,7 +5564,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>47.53002548217773</v>
+        <v>47.530029296875</v>
       </c>
       <c r="C194" t="n">
         <v>58.18999862670898</v>
@@ -5593,7 +5593,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>46.18230056762695</v>
+        <v>46.18230438232422</v>
       </c>
       <c r="C195" t="n">
         <v>56.54000091552734</v>
@@ -5622,7 +5622,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>43.7673454284668</v>
+        <v>43.76733779907227</v>
       </c>
       <c r="C196" t="n">
         <v>53.15000152587891</v>
@@ -5651,7 +5651,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>39.98761749267578</v>
+        <v>39.98762130737305</v>
       </c>
       <c r="C197" t="n">
         <v>48.56000137329102</v>
@@ -5680,7 +5680,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>43.70146560668945</v>
+        <v>43.70145797729492</v>
       </c>
       <c r="C198" t="n">
         <v>53.06999969482422</v>
@@ -5738,7 +5738,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>39.25278472900391</v>
+        <v>39.25278854370117</v>
       </c>
       <c r="C200" t="n">
         <v>47.20000076293945</v>
@@ -5825,7 +5825,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>35.71646118164062</v>
+        <v>35.71646499633789</v>
       </c>
       <c r="C203" t="n">
         <v>42.45000076293945</v>
@@ -5912,7 +5912,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>42.36972427368164</v>
+        <v>42.36972808837891</v>
       </c>
       <c r="C206" t="n">
         <v>49.79999923706055</v>
@@ -5999,7 +5999,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>29.55704879760742</v>
+        <v>29.55704307556152</v>
       </c>
       <c r="C209" t="n">
         <v>34.27999877929688</v>
@@ -6028,7 +6028,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.78050422668457</v>
+        <v>25.7805004119873</v>
       </c>
       <c r="C210" t="n">
         <v>29.89999961853027</v>
@@ -6057,7 +6057,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>28.91735649108887</v>
+        <v>28.91736030578613</v>
       </c>
       <c r="C211" t="n">
         <v>33.04000091552734</v>
@@ -6086,7 +6086,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>34.72883605957031</v>
+        <v>34.72883224487305</v>
       </c>
       <c r="C212" t="n">
         <v>39.68000030517578</v>
@@ -6115,7 +6115,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>31.97187995910645</v>
+        <v>31.97187232971191</v>
       </c>
       <c r="C213" t="n">
         <v>36.52999877929688</v>
@@ -6144,7 +6144,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>29.36833763122559</v>
+        <v>29.36833953857422</v>
       </c>
       <c r="C214" t="n">
         <v>33.06000137329102</v>
@@ -6173,7 +6173,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>28.32010078430176</v>
+        <v>28.32010269165039</v>
       </c>
       <c r="C215" t="n">
         <v>31.8799991607666</v>
@@ -6202,7 +6202,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>33.86330795288086</v>
+        <v>33.86331176757812</v>
       </c>
       <c r="C216" t="n">
         <v>38.11999893188477</v>
@@ -6231,7 +6231,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>38.88069534301758</v>
+        <v>38.88069915771484</v>
       </c>
       <c r="C217" t="n">
         <v>43.27999877929688</v>
@@ -6260,7 +6260,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>37.31756973266602</v>
+        <v>37.31756591796875</v>
       </c>
       <c r="C218" t="n">
         <v>41.54000091552734</v>
@@ -6318,7 +6318,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>40.61352920532227</v>
+        <v>40.613525390625</v>
       </c>
       <c r="C220" t="n">
         <v>44.70000076293945</v>
@@ -6347,7 +6347,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>36.91560745239258</v>
+        <v>36.91561126708984</v>
       </c>
       <c r="C221" t="n">
         <v>40.63000106811523</v>
@@ -6376,7 +6376,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>36.84291839599609</v>
+        <v>36.84291458129883</v>
       </c>
       <c r="C222" t="n">
         <v>40.54999923706055</v>
@@ -6405,7 +6405,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>36.52162551879883</v>
+        <v>36.52162933349609</v>
       </c>
       <c r="C223" t="n">
         <v>39.70000076293945</v>
@@ -6492,7 +6492,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>42.53650283813477</v>
+        <v>42.5364990234375</v>
       </c>
       <c r="C226" t="n">
         <v>45.72999954223633</v>
@@ -6521,7 +6521,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>44.93633270263672</v>
+        <v>44.93633651733398</v>
       </c>
       <c r="C227" t="n">
         <v>48.31000137329102</v>
@@ -6637,7 +6637,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>44.08160018920898</v>
+        <v>44.08160400390625</v>
       </c>
       <c r="C231" t="n">
         <v>46.90000152587891</v>
@@ -6666,7 +6666,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>40.15797424316406</v>
+        <v>40.1579704284668</v>
       </c>
       <c r="C232" t="n">
         <v>42.22000122070312</v>
@@ -6695,7 +6695,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>38.36978912353516</v>
+        <v>38.36978530883789</v>
       </c>
       <c r="C233" t="n">
         <v>40.34000015258789</v>
@@ -6753,7 +6753,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>43.51545715332031</v>
+        <v>43.51545333862305</v>
       </c>
       <c r="C235" t="n">
         <v>45.25</v>
@@ -6782,7 +6782,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>43.236572265625</v>
+        <v>43.23657608032227</v>
       </c>
       <c r="C236" t="n">
         <v>44.95999908447266</v>
@@ -6811,7 +6811,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>46.95823287963867</v>
+        <v>46.95822906494141</v>
       </c>
       <c r="C237" t="n">
         <v>48.83000183105469</v>
@@ -6840,7 +6840,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>46.97601699829102</v>
+        <v>46.97602081298828</v>
       </c>
       <c r="C238" t="n">
         <v>48.33000183105469</v>
@@ -6869,7 +6869,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>45.37224578857422</v>
+        <v>45.37224197387695</v>
       </c>
       <c r="C239" t="n">
         <v>46.68000030517578</v>
